--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487149_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487149_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0199</v>
+        <v>7.7185</v>
       </c>
       <c r="E2" t="n">
-        <v>8.375500000000001</v>
+        <v>8.2347</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3556</v>
+        <v>-0.5162</v>
       </c>
       <c r="G2" t="n">
         <v>9.5253</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5718</v>
+        <v>1.2704</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6795</v>
+        <v>0.5387</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8923</v>
+        <v>0.7317</v>
       </c>
       <c r="V2" t="n">
         <v>-2.4982</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9333</v>
+        <v>5.7017</v>
       </c>
       <c r="E3" t="n">
-        <v>5.32</v>
+        <v>5.5798</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3867</v>
+        <v>0.1219</v>
       </c>
       <c r="G3" t="n">
         <v>2.7697</v>
@@ -688,13 +688,13 @@
         <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0707</v>
+        <v>0.8391</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1216</v>
+        <v>0.1382</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1923</v>
+        <v>0.7009</v>
       </c>
       <c r="V3" t="n">
         <v>1.5138</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8322</v>
+        <v>4.9521</v>
       </c>
       <c r="E4" t="n">
-        <v>2.072</v>
+        <v>2.0313</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7602</v>
+        <v>2.9208</v>
       </c>
       <c r="G4" t="n">
         <v>4.8673</v>
@@ -766,13 +766,13 @@
         <v>1.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3159</v>
+        <v>0.4359</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0278</v>
+        <v>-0.0129</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2882</v>
+        <v>0.4488</v>
       </c>
       <c r="V4" t="n">
         <v>0.614</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.044</v>
+        <v>2.0906</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0586</v>
+        <v>0.1587</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9854</v>
+        <v>1.9319</v>
       </c>
       <c r="G5" t="n">
         <v>0.8912</v>
@@ -844,13 +844,13 @@
         <v>0.772</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3807</v>
+        <v>0.4273</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0449</v>
+        <v>0.0552</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4257</v>
+        <v>0.3721</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8639</v>
+        <v>0.8837</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1233</v>
+        <v>0.9826</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2595</v>
+        <v>-0.0989</v>
       </c>
       <c r="G6" t="n">
         <v>0.9294</v>
@@ -922,13 +922,13 @@
         <v>1.158</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0925</v>
+        <v>0.1124</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2353</v>
+        <v>0.0945</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1428</v>
+        <v>0.0178</v>
       </c>
       <c r="V6" t="n">
         <v>0.614</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.7931</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6688</v>
+        <v>0.5687</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1441</v>
+        <v>0.2244</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0506</v>
@@ -1000,13 +1000,13 @@
         <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7211</v>
+        <v>0.7013</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4442</v>
+        <v>0.3441</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2769</v>
+        <v>0.3573</v>
       </c>
       <c r="V7" t="n">
         <v>0.3704</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7793</v>
+        <v>0.699</v>
       </c>
       <c r="E8" t="n">
         <v>0.6824</v>
       </c>
       <c r="F8" t="n">
-        <v>0.097</v>
+        <v>0.0166</v>
       </c>
       <c r="G8" t="n">
         <v>0.669</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1104</v>
+        <v>0.0301</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1104</v>
+        <v>0.0301</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.468</v>
+        <v>-0.6296</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3593</v>
+        <v>2.5189</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8273</v>
+        <v>-3.1486</v>
       </c>
       <c r="G9" t="n">
         <v>0.6405999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0192</v>
+        <v>0.8576</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3543</v>
+        <v>0.5139</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6649</v>
+        <v>0.3437</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1278</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. GOMEZ FERNANDEZ</t>
+          <t>D. ARRIBAS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4687</v>
+        <v>-1.5082</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5967</v>
+        <v>-0.9812</v>
       </c>
       <c r="F10" t="n">
-        <v>1.128</v>
+        <v>-0.5269</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8646</v>
+        <v>-0.124</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8299</v>
+        <v>-0.1583</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9654</v>
+        <v>0.0343</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2515</v>
+        <v>0.1028</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5275</v>
+        <v>0.0621</v>
       </c>
       <c r="L10" t="n">
-        <v>0.724</v>
+        <v>0.0407</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1161</v>
+        <v>-0.2268</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.3574</v>
+        <v>-0.2204</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2413</v>
+        <v>-0.0064</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9301</v>
+        <v>-0.772</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.8602</v>
+        <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9301</v>
+        <v>0.193</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3259</v>
+        <v>-0.3262</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0119</v>
+        <v>-0.119</v>
       </c>
       <c r="U10" t="n">
-        <v>1.314</v>
+        <v>-0.2072</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. ARRIBAS RODRIGUEZ</t>
+          <t>L. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5885</v>
+        <v>-1.6432</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9812</v>
+        <v>-2.3964</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6072</v>
+        <v>0.7532</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.124</v>
+        <v>-0.8646</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1583</v>
+        <v>-1.8299</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0343</v>
+        <v>0.9654</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1028</v>
+        <v>1.2515</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0621</v>
+        <v>0.5275</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0407</v>
+        <v>0.724</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2268</v>
+        <v>-2.1161</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2204</v>
+        <v>-2.3574</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0064</v>
+        <v>0.2413</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.772</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="R11" t="n">
-        <v>0.193</v>
+        <v>1.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4065</v>
+        <v>1.1514</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.119</v>
+        <v>0.2122</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2875</v>
+        <v>0.9392</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>18.7604</v>
+        <v>19.0577</v>
       </c>
       <c r="E12" t="n">
-        <v>17.082</v>
+        <v>17.3795</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6784</v>
+        <v>1.678199999999999</v>
       </c>
       <c r="G12" t="n">
         <v>18.2533</v>
@@ -1372,7 +1372,7 @@
         <v>8.300599999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.009299999999999</v>
+        <v>-7.0093</v>
       </c>
       <c r="N12" t="n">
         <v>-10.8865</v>
@@ -1390,10 +1390,10 @@
         <v>11.5804</v>
       </c>
       <c r="S12" t="n">
-        <v>5.2017</v>
+        <v>5.499299999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4675</v>
+        <v>1.7649</v>
       </c>
       <c r="U12" t="n">
         <v>3.7344</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>P. HERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1858</v>
+        <v>1.8076</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4318</v>
+        <v>2.6236</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.246</v>
+        <v>-0.8161</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1467</v>
+        <v>4.4492</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6361</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4895</v>
+        <v>3.5394</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8172</v>
+        <v>5.0831</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1254</v>
+        <v>1.925</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6919</v>
+        <v>3.1581</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.6705</v>
+        <v>-0.6339</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4892</v>
+        <v>-1.0152</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.1813</v>
+        <v>0.3813</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.772</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1231</v>
+        <v>-1.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3511</v>
+        <v>1.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3318</v>
+        <v>-0.1857</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3239</v>
+        <v>-0.5294</v>
       </c>
       <c r="U13" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.3437</v>
       </c>
       <c r="V13" t="n">
-        <v>2.4793</v>
+        <v>-2.4559</v>
       </c>
       <c r="W13" t="n">
-        <v>2.4137</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.06560000000000001</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.886</v>
+        <v>1.7711</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5762</v>
+        <v>1.6763</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3099</v>
+        <v>0.0948</v>
       </c>
       <c r="G14" t="n">
         <v>1.4766</v>
@@ -1546,13 +1546,13 @@
         <v>1.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0813</v>
+        <v>-0.0337</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8196</v>
+        <v>-0.7194</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9009</v>
+        <v>0.6857</v>
       </c>
       <c r="V14" t="n">
         <v>0.3281</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ BLANCO</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0468</v>
+        <v>1.738</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0228</v>
+        <v>3.9311</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.976</v>
+        <v>-2.1931</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4492</v>
+        <v>0.1467</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9098000000000001</v>
+        <v>1.6361</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5394</v>
+        <v>-1.4895</v>
       </c>
       <c r="J15" t="n">
-        <v>5.0831</v>
+        <v>3.8172</v>
       </c>
       <c r="K15" t="n">
-        <v>1.925</v>
+        <v>3.1254</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1581</v>
+        <v>0.6919</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6339</v>
+        <v>-3.6705</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0152</v>
+        <v>-1.4892</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3813</v>
+        <v>-2.1813</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>-0.772</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9301</v>
+        <v>-2.1231</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9301</v>
+        <v>1.3511</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9465</v>
+        <v>-0.116</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1303</v>
+        <v>-0.1768</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1837</v>
+        <v>0.0608</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.4559</v>
+        <v>2.4793</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.4137</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4559</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0815</v>
+        <v>1.0833</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5721</v>
+        <v>2.173</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4906</v>
+        <v>-1.0897</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2173</v>
@@ -1702,13 +1702,13 @@
         <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5738</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2492</v>
+        <v>-0.6484</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3246</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>1.2936</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0556</v>
+        <v>0.3828</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4065</v>
+        <v>0.3063</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3508</v>
+        <v>0.0765</v>
       </c>
       <c r="G17" t="n">
         <v>-2.6114</v>
@@ -1780,13 +1780,13 @@
         <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3986</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0462</v>
+        <v>-0.1464</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3523</v>
+        <v>0.075</v>
       </c>
       <c r="V17" t="n">
         <v>1.9076</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.757</v>
+        <v>-0.7035</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0983</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6588000000000001</v>
+        <v>-0.6052</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5402</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2168</v>
+        <v>-0.1633</v>
       </c>
       <c r="T18" t="n">
         <v>-0.119</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0978</v>
+        <v>-0.0443</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9141</v>
+        <v>-2.1825</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1586</v>
+        <v>-1.2434</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0727</v>
+        <v>-0.9392</v>
       </c>
       <c r="G19" t="n">
         <v>-4.4002</v>
@@ -1936,13 +1936,13 @@
         <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>1.556</v>
+        <v>0.2876</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3617</v>
+        <v>-0.0403</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1943</v>
+        <v>0.3278</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.031</v>
+        <v>-3.6037</v>
       </c>
       <c r="E20" t="n">
         <v>-1.2522</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7788</v>
+        <v>-2.3514</v>
       </c>
       <c r="G20" t="n">
         <v>-4.4701</v>
@@ -2014,13 +2014,13 @@
         <v>0.965</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3986</v>
+        <v>0.0288</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0462</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3523</v>
+        <v>0.075</v>
       </c>
       <c r="V20" t="n">
         <v>0.06560000000000001</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1072</v>
+        <v>-3.6197</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3637</v>
+        <v>-2.0632</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7435</v>
+        <v>-1.5565</v>
       </c>
       <c r="G21" t="n">
         <v>-3.02</v>
@@ -2092,13 +2092,13 @@
         <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7667</v>
+        <v>-0.2793</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5949</v>
+        <v>-0.2945</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1719</v>
+        <v>0.0152</v>
       </c>
       <c r="V21" t="n">
         <v>0.06560000000000001</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8888</v>
+        <v>-4.1403</v>
       </c>
       <c r="E22" t="n">
         <v>-1.9063</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9825</v>
+        <v>-2.2339</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6799</v>
@@ -2170,13 +2170,13 @@
         <v>1.158</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2089</v>
+        <v>-0.4604</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0437</v>
+        <v>-0.2952</v>
       </c>
       <c r="V22" t="n">
         <v>-1.228</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.3178</v>
+        <v>-8.6228</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.2256</v>
+        <v>-5.825</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0922</v>
+        <v>-2.7978</v>
       </c>
       <c r="G23" t="n">
         <v>-7.3866</v>
@@ -2248,13 +2248,13 @@
         <v>1.3511</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.661</v>
+        <v>-0.966</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2492</v>
+        <v>-0.8487</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4118</v>
+        <v>-0.1173</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6562</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-18.7602</v>
+        <v>-16.0897</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.678099999999999</v>
+        <v>-1.6781</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.082</v>
+        <v>-14.4116</v>
       </c>
       <c r="G24" t="n">
         <v>-18.2532</v>
@@ -2326,13 +2326,13 @@
         <v>14.4757</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.2018</v>
+        <v>-2.5315</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.7342</v>
+        <v>-3.7343</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4676</v>
+        <v>1.2027</v>
       </c>
       <c r="V24" t="n">
         <v>1.7997</v>
